--- a/02 Output/FAB_file.xlsx
+++ b/02 Output/FAB_file.xlsx
@@ -93,6 +93,45 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="904875"/>
+          <a:ext cx="1219370" cy="1219370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -137,6 +176,45 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="904875"/>
+          <a:ext cx="1219370" cy="1219370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -181,6 +259,45 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="904875"/>
+          <a:ext cx="1219370" cy="1219370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -208,6 +325,45 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="904875"/>
+          <a:ext cx="1219370" cy="1219370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>

--- a/02 Output/FAB_file.xlsx
+++ b/02 Output/FAB_file.xlsx
@@ -10,9 +10,84 @@
     <sheet name="Behaviors CSMOKING" sheetId="2" r:id="rId3"/>
     <sheet name="Behaviors LPA" sheetId="3" r:id="rId4"/>
     <sheet name="Behaviors SLEEP" sheetId="4" r:id="rId5"/>
+    <sheet name="Top  5 Outcomes" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="81" uniqueCount="23">
+  <si>
+    <t>counties</t>
+  </si>
+  <si>
+    <t>Bullock-AL</t>
+  </si>
+  <si>
+    <t>East Carroll-LA</t>
+  </si>
+  <si>
+    <t>McDowell-WV</t>
+  </si>
+  <si>
+    <t>Mingo-WV</t>
+  </si>
+  <si>
+    <t>Todd-SD</t>
+  </si>
+  <si>
+    <t>rank_top5</t>
+  </si>
+  <si>
+    <t>measure</t>
+  </si>
+  <si>
+    <t>High blood pressure among adults</t>
+  </si>
+  <si>
+    <t>Obesity among adults</t>
+  </si>
+  <si>
+    <t>High cholesterol among adults who have ever been screened</t>
+  </si>
+  <si>
+    <t>All teeth lost among adults aged &gt;=65 years</t>
+  </si>
+  <si>
+    <t>Arthritis among adults</t>
+  </si>
+  <si>
+    <t>Depression among adults</t>
+  </si>
+  <si>
+    <t>measureid</t>
+  </si>
+  <si>
+    <t>BPHIGH</t>
+  </si>
+  <si>
+    <t>OBESITY</t>
+  </si>
+  <si>
+    <t>HIGHCHOL</t>
+  </si>
+  <si>
+    <t>TEETHLOST</t>
+  </si>
+  <si>
+    <t>ARTHRITIS</t>
+  </si>
+  <si>
+    <t>DEPRESSION</t>
+  </si>
+  <si>
+    <t>prevalence_percent</t>
+  </si>
+  <si>
+    <t>outcome_frequency</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31,7 +106,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -39,12 +114,14 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -62,10 +139,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -93,6 +170,11 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -105,50 +187,6 @@
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="904875"/>
-          <a:ext cx="1219370" cy="1219370"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -176,6 +214,11 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -188,50 +231,6 @@
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="904875"/>
-          <a:ext cx="1219370" cy="1219370"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -259,6 +258,11 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -271,50 +275,6 @@
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="904875"/>
-          <a:ext cx="1219370" cy="1219370"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -342,45 +302,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="904875"/>
-          <a:ext cx="1219370" cy="1219370"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -418,4 +339,533 @@
   <sheetData/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1">
+        <v>52.400001525878906</v>
+      </c>
+      <c r="F2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1">
+        <v>51</v>
+      </c>
+      <c r="F3" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1">
+        <v>37.099998474121094</v>
+      </c>
+      <c r="F4" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1">
+        <v>35.099998474121094</v>
+      </c>
+      <c r="F5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1">
+        <v>30.600000381469727</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1">
+        <v>51.700000762939453</v>
+      </c>
+      <c r="F8" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="1">
+        <v>43.5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="1">
+        <v>35.400001525878906</v>
+      </c>
+      <c r="F10" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="1">
+        <v>30.299999237060547</v>
+      </c>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="1">
+        <v>46.099998474121094</v>
+      </c>
+      <c r="F12" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="1">
+        <v>44.599998474121094</v>
+      </c>
+      <c r="F13" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="1">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="1">
+        <v>37.099998474121094</v>
+      </c>
+      <c r="F14" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="1">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="1">
+        <v>35.099998474121094</v>
+      </c>
+      <c r="F15" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="1">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="1">
+        <v>34.200000762939453</v>
+      </c>
+      <c r="F16" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1">
+        <v>43</v>
+      </c>
+      <c r="F17" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="1">
+        <v>42.799999237060547</v>
+      </c>
+      <c r="F18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="1">
+        <v>37.900001525878906</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="1">
+        <v>36</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="1">
+        <v>35</v>
+      </c>
+      <c r="F21" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1">
+        <v>50.200000762939453</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="1">
+        <v>44.5</v>
+      </c>
+      <c r="F23" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="1">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="1">
+        <v>41.700000762939453</v>
+      </c>
+      <c r="F24" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="1">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="1">
+        <v>30.100000381469727</v>
+      </c>
+      <c r="F25" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="1">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="1">
+        <v>29.700000762939453</v>
+      </c>
+      <c r="F26" s="1">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/02 Output/FAB_file.xlsx
+++ b/02 Output/FAB_file.xlsx
@@ -7,17 +7,32 @@
   </bookViews>
   <sheets>
     <sheet name="Behaviors BINGE" sheetId="1" r:id="rId2"/>
-    <sheet name="Behaviors CSMOKING" sheetId="2" r:id="rId3"/>
-    <sheet name="Behaviors LPA" sheetId="3" r:id="rId4"/>
-    <sheet name="Behaviors SLEEP" sheetId="4" r:id="rId5"/>
-    <sheet name="Top  5 Outcomes" sheetId="5" r:id="rId6"/>
+    <sheet name="Behaviors CSMOKING" sheetId="2" r:id="rId4"/>
+    <sheet name="Behaviors LPA" sheetId="3" r:id="rId5"/>
+    <sheet name="Behaviors SLEEP" sheetId="4" r:id="rId6"/>
+    <sheet name="Health Outcomes" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="81" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="97" uniqueCount="36">
+  <si>
+    <t>Top 20 Counties for BINGE</t>
+  </si>
+  <si>
+    <t>Statistics: Age-adjusted prevalence,reproted as percentage</t>
+  </si>
+  <si>
+    <t>Top 20 Counties for CSMOKING</t>
+  </si>
+  <si>
+    <t>Top 20 Counties for LPA</t>
+  </si>
+  <si>
+    <t>Top 20 Counties for SLEEP</t>
+  </si>
   <si>
     <t>counties</t>
   </si>
@@ -86,16 +101,178 @@
   </si>
   <si>
     <t>outcome_frequency</t>
+  </si>
+  <si>
+    <t>County</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Health Outcome</t>
+  </si>
+  <si>
+    <t>Measure ID</t>
+  </si>
+  <si>
+    <t>Age-adjusted Prevalence (%)</t>
+  </si>
+  <si>
+    <t>Outcome Frequency</t>
+  </si>
+  <si>
+    <t>statistics note:</t>
+  </si>
+  <si>
+    <t>Prevalence is age-adjusted and reported as a percentage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="33">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -106,7 +283,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -114,14 +291,256 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
     <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -133,16 +552,16 @@
 <xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -177,16 +596,16 @@
 <xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -221,16 +640,16 @@
 <xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -265,16 +684,16 @@
 <xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -307,562 +726,614 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1">
-        <v>52.400001525878906</v>
-      </c>
-      <c r="F2" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1">
-        <v>51</v>
-      </c>
-      <c r="F3" s="1">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="1">
-        <v>37.099998474121094</v>
-      </c>
-      <c r="F4" s="1">
-        <v>5</v>
+      <c r="A4" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1">
-        <v>35.099998474121094</v>
-      </c>
-      <c r="F5" s="1">
-        <v>4</v>
+        <v>20</v>
+      </c>
+      <c r="E5" s="5">
+        <v>52.400001525878906</v>
+      </c>
+      <c r="F5" s="5">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1">
-        <v>30.600000381469727</v>
-      </c>
-      <c r="F6" s="1">
+        <v>21</v>
+      </c>
+      <c r="E6" s="5">
+        <v>51</v>
+      </c>
+      <c r="F6" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1">
-        <v>52.5</v>
-      </c>
-      <c r="F7" s="1">
+        <v>22</v>
+      </c>
+      <c r="E7" s="5">
+        <v>37.099998474121094</v>
+      </c>
+      <c r="F7" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="B8" s="5">
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="1">
-        <v>51.700000762939453</v>
-      </c>
-      <c r="F8" s="1">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="E8" s="5">
+        <v>35.099998474121094</v>
+      </c>
+      <c r="F8" s="5">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="1">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="B9" s="5">
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="1">
-        <v>43.5</v>
-      </c>
-      <c r="F9" s="1">
-        <v>4</v>
+        <v>24</v>
+      </c>
+      <c r="E9" s="5">
+        <v>30.600000381469727</v>
+      </c>
+      <c r="F9" s="5">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="1">
-        <v>35.400001525878906</v>
-      </c>
-      <c r="F10" s="1">
+        <v>20</v>
+      </c>
+      <c r="E10" s="5">
+        <v>52.5</v>
+      </c>
+      <c r="F10" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5">
         <v>2</v>
       </c>
-      <c r="B11" s="1">
-        <v>5</v>
-      </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="1">
-        <v>30.299999237060547</v>
-      </c>
-      <c r="F11" s="1">
+        <v>21</v>
+      </c>
+      <c r="E11" s="5">
+        <v>51.700000762939453</v>
+      </c>
+      <c r="F11" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5">
         <v>3</v>
       </c>
-      <c r="B12" s="1">
-        <v>1</v>
-      </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="1">
-        <v>46.099998474121094</v>
-      </c>
-      <c r="F12" s="1">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="E12" s="5">
+        <v>43.5</v>
+      </c>
+      <c r="F12" s="5">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="1">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="B13" s="5">
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="1">
-        <v>44.599998474121094</v>
-      </c>
-      <c r="F13" s="1">
+        <v>22</v>
+      </c>
+      <c r="E13" s="5">
+        <v>35.400001525878906</v>
+      </c>
+      <c r="F13" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="1">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="B14" s="5">
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="1">
-        <v>37.099998474121094</v>
-      </c>
-      <c r="F14" s="1">
+        <v>24</v>
+      </c>
+      <c r="E14" s="5">
+        <v>30.299999237060547</v>
+      </c>
+      <c r="F14" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="1">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="B15" s="5">
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="1">
-        <v>35.099998474121094</v>
-      </c>
-      <c r="F15" s="1">
+        <v>21</v>
+      </c>
+      <c r="E15" s="5">
+        <v>46.099998474121094</v>
+      </c>
+      <c r="F15" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="1">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B16" s="5">
+        <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="1">
-        <v>34.200000762939453</v>
-      </c>
-      <c r="F16" s="1">
-        <v>4</v>
+        <v>20</v>
+      </c>
+      <c r="E16" s="5">
+        <v>44.599998474121094</v>
+      </c>
+      <c r="F16" s="5">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="B17" s="5">
+        <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="1">
-        <v>43</v>
-      </c>
-      <c r="F17" s="1">
+        <v>22</v>
+      </c>
+      <c r="E17" s="5">
+        <v>37.099998474121094</v>
+      </c>
+      <c r="F17" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="5">
         <v>4</v>
       </c>
-      <c r="B18" s="1">
-        <v>2</v>
-      </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="1">
-        <v>42.799999237060547</v>
-      </c>
-      <c r="F18" s="1">
+        <v>24</v>
+      </c>
+      <c r="E18" s="5">
+        <v>35.099998474121094</v>
+      </c>
+      <c r="F18" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="5">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="5">
+        <v>34.200000762939453</v>
+      </c>
+      <c r="F19" s="5">
         <v>4</v>
-      </c>
-      <c r="B19" s="1">
-        <v>3</v>
-      </c>
-      <c r="C19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="1">
-        <v>37.900001525878906</v>
-      </c>
-      <c r="F19" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="1">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="B20" s="5">
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="1">
-        <v>36</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="E20" s="5">
+        <v>43</v>
+      </c>
+      <c r="F20" s="5">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="1">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B21" s="5">
+        <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="1">
-        <v>35</v>
-      </c>
-      <c r="F21" s="1">
+        <v>20</v>
+      </c>
+      <c r="E21" s="5">
+        <v>42.799999237060547</v>
+      </c>
+      <c r="F21" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B22" s="5">
+        <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="1">
-        <v>50.200000762939453</v>
-      </c>
-      <c r="F22" s="1">
+        <v>22</v>
+      </c>
+      <c r="E22" s="5">
+        <v>37.900001525878906</v>
+      </c>
+      <c r="F22" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="B23" s="5">
+        <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="1">
-        <v>44.5</v>
-      </c>
-      <c r="F23" s="1">
-        <v>4</v>
+        <v>25</v>
+      </c>
+      <c r="E23" s="5">
+        <v>36</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="1">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="B24" s="5">
+        <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="1">
-        <v>41.700000762939453</v>
-      </c>
-      <c r="F24" s="1">
+        <v>24</v>
+      </c>
+      <c r="E24" s="5">
+        <v>35</v>
+      </c>
+      <c r="F24" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="1">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="B25" s="5">
+        <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="1">
-        <v>30.100000381469727</v>
-      </c>
-      <c r="F25" s="1">
+        <v>21</v>
+      </c>
+      <c r="E25" s="5">
+        <v>50.200000762939453</v>
+      </c>
+      <c r="F25" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="1">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="B26" s="5">
+        <v>2</v>
       </c>
       <c r="C26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="5">
+        <v>44.5</v>
+      </c>
+      <c r="F26" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
         <v>10</v>
       </c>
-      <c r="D26" t="s">
+      <c r="B27" s="5">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="5">
+        <v>41.700000762939453</v>
+      </c>
+      <c r="F27" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="5">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="1">
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="5">
+        <v>30.100000381469727</v>
+      </c>
+      <c r="F28" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="5">
+        <v>5</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="5">
         <v>29.700000762939453</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F29" s="5">
         <v>5</v>
       </c>
     </row>
